--- a/data/final/contracts.xlsx
+++ b/data/final/contracts.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="67">
   <si>
     <t>player</t>
   </si>
@@ -98,18 +98,6 @@
     <t>780,000 </t>
   </si>
   <si>
-    <t>Daniel Gore</t>
-  </si>
-  <si>
-    <t>3,000 </t>
-  </si>
-  <si>
-    <t>156,000 </t>
-  </si>
-  <si>
-    <t>Diego León</t>
-  </si>
-  <si>
     <t>Diogo Dalot</t>
   </si>
   <si>
@@ -119,33 +107,6 @@
     <t>4,420,000 </t>
   </si>
   <si>
-    <t>Elyh Harrison</t>
-  </si>
-  <si>
-    <t>1,000 </t>
-  </si>
-  <si>
-    <t>52,000 </t>
-  </si>
-  <si>
-    <t>Ethan Ennis</t>
-  </si>
-  <si>
-    <t>Ethan Wheatley</t>
-  </si>
-  <si>
-    <t>5,000 </t>
-  </si>
-  <si>
-    <t>260,000 </t>
-  </si>
-  <si>
-    <t>Ethan Williams</t>
-  </si>
-  <si>
-    <t>Habeeb Ogunneye</t>
-  </si>
-  <si>
     <t>Harry Maguire</t>
   </si>
   <si>
@@ -155,18 +116,6 @@
     <t>9,880,000 </t>
   </si>
   <si>
-    <t>Jadon Sancho</t>
-  </si>
-  <si>
-    <t>50,000 </t>
-  </si>
-  <si>
-    <t>2,600,000 </t>
-  </si>
-  <si>
-    <t>Joe Hugill</t>
-  </si>
-  <si>
     <t>Joshua Zirkzee</t>
   </si>
   <si>
@@ -236,15 +185,6 @@
     <t>2,080,000 </t>
   </si>
   <si>
-    <t>Radek Vítek</t>
-  </si>
-  <si>
-    <t>1,500 </t>
-  </si>
-  <si>
-    <t>78,000 </t>
-  </si>
-  <si>
     <t>Senne Lammens</t>
   </si>
   <si>
@@ -252,15 +192,6 @@
   </si>
   <si>
     <t>3,120,000 </t>
-  </si>
-  <si>
-    <t>Sonny Aljofree</t>
-  </si>
-  <si>
-    <t>750 </t>
-  </si>
-  <si>
-    <t>39,000 </t>
   </si>
   <si>
     <t>Tom Heaton</t>
@@ -342,7 +273,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -481,29 +412,33 @@
       <c r="C10" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D10"/>
+      <c r="D10" s="2" t="n">
+        <v>3.5E7</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11"/>
+        <v>33</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>1.3E7</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>3.5E7</v>
@@ -511,101 +446,115 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13"/>
+        <v>12</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>5.0E7</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
         <v>38</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14"/>
+        <v>40</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>5.5E7</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15"/>
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>4.5E7</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16"/>
+        <v>21</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>1.6E7</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
         <v>43</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17"/>
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>4.5E7</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
         <v>44</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1.3E7</v>
+        <v>2.8E7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D19"/>
+      <c r="D19" s="2" t="n">
+        <v>6.0E7</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20"/>
+      <c r="D20" s="2" t="n">
+        <v>4.0E7</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
@@ -618,7 +567,7 @@
         <v>53</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>3.5E7</v>
+        <v>2.5E7</v>
       </c>
     </row>
     <row r="22">
@@ -626,216 +575,68 @@
         <v>54</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>5.0E7</v>
+        <v>2.5E7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>5.5E7</v>
+        <v>9000000.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24"/>
+        <v>62</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>200000.0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>1.6E7</v>
+        <v>3000000.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>4.5E7</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>2.8E7</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>6.0E7</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>4.0E7</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>2.5E7</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>2.5E7</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D32"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>9000000.0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D34"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>200000.0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>3000000.0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D37" s="2" t="n">
         <v>1.2E7</v>
       </c>
     </row>
